--- a/data/04_Resultados/resultados_tesis.xlsx
+++ b/data/04_Resultados/resultados_tesis.xlsx
@@ -7,11 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tabla9_mesa" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tabla9_zona_focal" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tabla9_puesto" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tabla9_nuevos_vs_historia" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zona_focal_por_barrio" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tabla10_mesa" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tabla10_zona_focal" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tabla10_puesto" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tabla12_nuevos_vs_historia" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tabla13_zona_focal_por_barrio" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CV_2019" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensibilidad" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OE1_puestos" sheetId="8" state="visible" r:id="rId8"/>
@@ -20,6 +20,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables_puesto" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mesas_atipicas" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Predicciones_2023" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tabla10_lineas_base" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tabla10_puesto_ampliada" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC_vs_lineas_base" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tabla8_spearman_p" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nota_ampliacion" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -88,11 +93,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -15808,6 +15815,1022 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Modelo</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>MAE (p. p.)</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>RMSE (p. p.)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Sesgo (p. p.)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Accuracy</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Precision</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Recall</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Media de la localidad 2019</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>9.336</v>
+      </c>
+      <c r="C2" t="n">
+        <v>11.736</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.547</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.547</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.707</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Persistencia por puesto (tasa de 2019)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>9.221</v>
+      </c>
+      <c r="C3" t="n">
+        <v>11.868</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.574</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.652</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.706</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.663</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Modelo</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>MAE (p. p.)</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>RMSE (p. p.)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Sesgo (p. p.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Persistencia (tasa de 2019)</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>7.307</v>
+      </c>
+      <c r="C2" t="n">
+        <v>9.827</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-1.246</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Regresión logística</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>25.295</v>
+      </c>
+      <c r="C3" t="n">
+        <v>36.951</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-17.073</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Random Forest</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="C4" t="n">
+        <v>10.458</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.349</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gradient Boosting</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>9.076000000000001</v>
+      </c>
+      <c r="C5" t="n">
+        <v>11.879</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-1.434</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Red neuronal feedforward (FNN)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>9.785</v>
+      </c>
+      <c r="C6" t="n">
+        <v>11.098</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3.114</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Clasificador base sin interacción vecinal (α = 1)</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>8.151</v>
+      </c>
+      <c r="C7" t="n">
+        <v>10.452</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.372</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Modelo híbrido ML + ABM + SIG (r = 300 m, α = 0.8)</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>8.141</v>
+      </c>
+      <c r="C8" t="n">
+        <v>10.421</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.367</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Media de la localidad 2019</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="C9" t="n">
+        <v>8.683</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-3.184</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Persistencia por puesto (tasa de 2019)</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>7.213</v>
+      </c>
+      <c r="C10" t="n">
+        <v>9.965</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-1.525</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nivel</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Modelo</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Frente a</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Dif. MAE (p. p.)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>IC95 inf</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>IC95 sup</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Incluye 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Mesa (n = 351)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Random Forest</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Persistencia (tasa de 2019)</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.668</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-1.777</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="G2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Puesto (n = 15)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Random Forest</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Persistencia (tasa de 2019)</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.832</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-0.959</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2.414</v>
+      </c>
+      <c r="G3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Mesa (n = 351)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Random Forest</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Media de la localidad 2019</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-1.523</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-2.436</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-0.447</v>
+      </c>
+      <c r="G4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Puesto (n = 15)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Random Forest</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Media de la localidad 2019</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.062</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4.309</v>
+      </c>
+      <c r="G5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Mesa (n = 351)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Random Forest</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Persistencia por puesto (tasa de 2019)</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-1.408</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-2.314</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-0.464</v>
+      </c>
+      <c r="G6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Puesto (n = 15)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Random Forest</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Persistencia por puesto (tasa de 2019)</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.927</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-1.029</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2.792</v>
+      </c>
+      <c r="G7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Mesa (n = 351)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Modelo híbrido ML + ABM + SIG (r = 300 m, α = 0.8)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Persistencia (tasa de 2019)</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-1.824</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="G8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Puesto (n = 15)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Modelo híbrido ML + ABM + SIG (r = 300 m, α = 0.8)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Persistencia (tasa de 2019)</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.834</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-0.896</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.326</v>
+      </c>
+      <c r="G9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Mesa (n = 351)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Modelo híbrido ML + ABM + SIG (r = 300 m, α = 0.8)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Media de la localidad 2019</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-1.545</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-2.414</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="G10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Puesto (n = 15)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Modelo híbrido ML + ABM + SIG (r = 300 m, α = 0.8)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Media de la localidad 2019</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2.091</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="G11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Mesa (n = 351)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Modelo híbrido ML + ABM + SIG (r = 300 m, α = 0.8)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Persistencia por puesto (tasa de 2019)</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-1.431</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-2.353</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-0.434</v>
+      </c>
+      <c r="G12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Puesto (n = 15)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Modelo híbrido ML + ABM + SIG (r = 300 m, α = 0.8)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Persistencia por puesto (tasa de 2019)</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.928</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-1.048</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.644</v>
+      </c>
+      <c r="G13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>rho</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>p_BH</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Significativa (p_BH &lt; 0,05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>p_mujeres_cnpv</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>-0.8364</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.0135</v>
+      </c>
+      <c r="E2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>p_edu_superior</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>-0.6182</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.0426</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.1848</v>
+      </c>
+      <c r="E3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>p_65_mas</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>-0.5182</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.1025</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.218</v>
+      </c>
+      <c r="E4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>p_mujeres</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>-0.5182</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.1025</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.218</v>
+      </c>
+      <c r="E5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>p_41_60</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>-0.4727</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.218</v>
+      </c>
+      <c r="E6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>p_estrato_alto</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>-0.3091</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.3846</v>
+      </c>
+      <c r="E7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>p_60_mas</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>-0.2273</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.5014999999999999</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.5014999999999999</v>
+      </c>
+      <c r="E8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>densidad</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.2716</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="E9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>p_estrato_bajo</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.3909</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.2345</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.3049</v>
+      </c>
+      <c r="E10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>dist_puesto_m</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.4636</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.1509</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.218</v>
+      </c>
+      <c r="E11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>p_26_40</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.4909</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.1252</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.218</v>
+      </c>
+      <c r="E12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>p_18_25</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.5727</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.0655</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.213</v>
+      </c>
+      <c r="E13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>p_20_29</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.8182</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.0021</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.0135</v>
+      </c>
+      <c r="E14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nota</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Las hojas Tabla10_lineas_base, Tabla10_puesto_ampliada, IC_vs_lineas_base y Tabla8_spearman_p se calcularon a partir de Predicciones_2023, Variables_puesto y OE1_puestos de esta misma ejecución (Colab, 9-oct-2026), sin reentrenar los modelos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>IC 95 %: bootstrap por conglomerados (puestos), 2.000 remuestreos, semilla 1042. Valores p de Spearman corregidos por Benjamini-Hochberg.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Las demás hojas no se modificaron; solo se renombraron Tabla9_* a Tabla10_*/Tabla12_*/Tabla13_* según la numeración del documento.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -16142,7 +17165,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n"/>
+      <c r="A3" s="2" t="n"/>
       <c r="B3" s="1" t="inlineStr">
         <is>
           <t>Regresión logística</t>
@@ -16159,7 +17182,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n"/>
+      <c r="A4" s="2" t="n"/>
       <c r="B4" s="1" t="inlineStr">
         <is>
           <t>Random Forest</t>
@@ -16176,7 +17199,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n"/>
+      <c r="A5" s="2" t="n"/>
       <c r="B5" s="1" t="inlineStr">
         <is>
           <t>Gradient Boosting</t>
@@ -16193,7 +17216,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n"/>
+      <c r="A6" s="2" t="n"/>
       <c r="B6" s="1" t="inlineStr">
         <is>
           <t>Red neuronal feedforward (FNN)</t>
@@ -16210,7 +17233,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n"/>
+      <c r="A7" s="2" t="n"/>
       <c r="B7" s="1" t="inlineStr">
         <is>
           <t>Clasificador base sin interacción vecinal (α = 1)</t>
@@ -16227,7 +17250,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n"/>
+      <c r="A8" s="3" t="n"/>
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>Modelo híbrido ML + ABM + SIG (r = 300 m, α = 0.8)</t>
@@ -16265,7 +17288,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n"/>
+      <c r="A10" s="2" t="n"/>
       <c r="B10" s="1" t="inlineStr">
         <is>
           <t>Regresión logística</t>
@@ -16282,7 +17305,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n"/>
+      <c r="A11" s="2" t="n"/>
       <c r="B11" s="1" t="inlineStr">
         <is>
           <t>Random Forest</t>
@@ -16299,7 +17322,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n"/>
+      <c r="A12" s="2" t="n"/>
       <c r="B12" s="1" t="inlineStr">
         <is>
           <t>Gradient Boosting</t>
@@ -16316,7 +17339,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n"/>
+      <c r="A13" s="2" t="n"/>
       <c r="B13" s="1" t="inlineStr">
         <is>
           <t>Red neuronal feedforward (FNN)</t>
@@ -16333,7 +17356,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n"/>
+      <c r="A14" s="2" t="n"/>
       <c r="B14" s="1" t="inlineStr">
         <is>
           <t>Clasificador base sin interacción vecinal (α = 1)</t>
@@ -16350,7 +17373,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n"/>
+      <c r="A15" s="3" t="n"/>
       <c r="B15" s="1" t="inlineStr">
         <is>
           <t>Modelo híbrido ML + ABM + SIG (r = 300 m, α = 0.8)</t>
@@ -16415,7 +17438,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n"/>
+      <c r="A3" s="3" t="n"/>
       <c r="B3" s="1" t="inlineStr">
         <is>
           <t>Modelo híbrido ML + ABM + SIG (r = 300 m, α = 0.8)</t>
@@ -16447,7 +17470,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n"/>
+      <c r="A5" s="3" t="n"/>
       <c r="B5" s="1" t="inlineStr">
         <is>
           <t>Modelo híbrido ML + ABM + SIG (r = 300 m, α = 0.8)</t>
@@ -16479,7 +17502,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n"/>
+      <c r="A7" s="3" t="n"/>
       <c r="B7" s="1" t="inlineStr">
         <is>
           <t>Modelo híbrido ML + ABM + SIG (r = 300 m, α = 0.8)</t>
@@ -16511,7 +17534,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n"/>
+      <c r="A9" s="3" t="n"/>
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>Modelo híbrido ML + ABM + SIG (r = 300 m, α = 0.8)</t>
@@ -16543,7 +17566,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n"/>
+      <c r="A11" s="3" t="n"/>
       <c r="B11" s="1" t="inlineStr">
         <is>
           <t>Modelo híbrido ML + ABM + SIG (r = 300 m, α = 0.8)</t>
@@ -16928,7 +17951,6 @@
           <t>COLEGIO LICEO DE CERVANTES</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -16947,7 +17969,6 @@
           <t>COLEGIO EL BUEN CONCEJO</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -16989,7 +18010,6 @@
           <t>UNIVERSIDAD AUTONOMA DEL CARIBE</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16997,7 +18017,6 @@
           <t>R04</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
         <v>0.6385</v>
       </c>
@@ -17018,7 +18037,6 @@
           <t>R05</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
         <v>0.7663</v>
       </c>
@@ -17039,7 +18057,6 @@
           <t>R06</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
         <v>0.6404</v>
       </c>
@@ -17140,7 +18157,6 @@
           <t>COLEGIO LA MEDALLA MILAGROSA</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -17159,7 +18175,6 @@
           <t>COLEGIO BIFI LA SALLE</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -17178,7 +18193,6 @@
           <t>COL.LA ENSEÑANZA</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -17186,7 +18200,6 @@
           <t>R13</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
         <v>0.8187</v>
       </c>
@@ -17195,7 +18208,6 @@
           <t>CENTRO COMERCIAL VIVA BARRANQUILLA</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">

--- a/data/04_Resultados/resultados_tesis.xlsx
+++ b/data/04_Resultados/resultados_tesis.xlsx
@@ -16808,7 +16808,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Las hojas Tabla10_lineas_base, Tabla10_puesto_ampliada, IC_vs_lineas_base y Tabla8_spearman_p se calcularon a partir de Predicciones_2023, Variables_puesto y OE1_puestos de esta misma ejecución (Colab, 9-oct-2026), sin reentrenar los modelos.</t>
+          <t>Las hojas Tabla10_lineas_base, Tabla10_puesto_ampliada, IC_vs_lineas_base y Tabla8_spearman_p las genera la sección 8 del cuaderno a partir de Predicciones_2023, Variables_puesto y OE1_puestos de esta misma ejecución, sin reentrenar los modelos.</t>
         </is>
       </c>
     </row>
@@ -16822,7 +16822,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Las demás hojas no se modificaron; solo se renombraron Tabla9_* a Tabla10_*/Tabla12_*/Tabla13_* según la numeración del documento.</t>
+          <t>Las hojas Tabla9_* se renombran como Tabla10_*/Tabla12_*/Tabla13_* según la numeración del documento.</t>
         </is>
       </c>
     </row>
